--- a/assets/downloads/ImportMalavi_Template_2026-07.xlsx
+++ b/assets/downloads/ImportMalavi_Template_2026-07.xlsx
@@ -966,7 +966,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - Use the same reference key everywhere. 'Gupta et al 2019' on one sheet and 'Gupta et al 2020' on another is the single most common error we see.</t>
+          <t xml:space="preserve">  - Use the same reference key everywhere, e.g., Gupta et al. 2019</t>
         </is>
       </c>
     </row>
